--- a/artfynd/A 56504-2025 artfynd.xlsx
+++ b/artfynd/A 56504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16886943</v>
+        <v>16886945</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5900 m OSO Hedberg, Pi lm</t>
+          <t>5900 m SO Hedberg, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681741.8583550726</v>
+        <v>681633</v>
       </c>
       <c r="R2" t="n">
-        <v>7258332.122441174</v>
+        <v>7258095</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,6 +774,414 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16885438</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5800 m SO Hedberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>681461</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7258027</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16886944</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5900 m SO Hedberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>681633</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7258094</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-09-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16886942</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5900 m SO Hedberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>681610</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7258198</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-09-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16886943</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5900 m OSO Hedberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>681742</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7258332</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-09-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56504-2025 artfynd.xlsx
+++ b/artfynd/A 56504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16886945</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16885438</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16886944</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16886942</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16886943</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>